--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DDV_HRM-2031-0100/Panel-28/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DDV_HRM-2031-0100/Panel-28/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.66902</v>
+        <v>16.78309</v>
       </c>
       <c r="D3" t="n">
         <v>16.41778</v>
       </c>
       <c r="E3" t="n">
-        <v>16.78309</v>
+        <v>16.66902</v>
       </c>
       <c r="F3" t="n">
         <v>42.31678</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>16.65875</v>
+      </c>
+      <c r="D7" t="n">
         <v>16.22343</v>
-      </c>
-      <c r="D7" t="n">
-        <v>16.65875</v>
       </c>
       <c r="E7" t="n">
         <v>16.47155</v>
@@ -613,10 +613,10 @@
         <v>16.69854</v>
       </c>
       <c r="D8" t="n">
+        <v>16.2754</v>
+      </c>
+      <c r="E8" t="n">
         <v>16.54926</v>
-      </c>
-      <c r="E8" t="n">
-        <v>16.2754</v>
       </c>
       <c r="F8" t="n">
         <v>42.03935</v>
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.44766</v>
+        <v>16.71845</v>
       </c>
       <c r="D9" t="n">
         <v>16.14828</v>
       </c>
       <c r="E9" t="n">
-        <v>16.71845</v>
+        <v>16.44766</v>
       </c>
       <c r="F9" t="n">
         <v>42.65807</v>
@@ -660,13 +660,13 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>16.71155</v>
+      </c>
+      <c r="D10" t="n">
         <v>16.35087</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>16.38145</v>
-      </c>
-      <c r="E10" t="n">
-        <v>16.71155</v>
       </c>
       <c r="F10" t="n">
         <v>42.74891</v>
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16.63094</v>
+        <v>16.72479</v>
       </c>
       <c r="D11" t="n">
         <v>16.55807</v>
       </c>
       <c r="E11" t="n">
-        <v>16.72479</v>
+        <v>16.63094</v>
       </c>
       <c r="F11" t="n">
         <v>42.07506</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.72374</v>
+        <v>17.06103</v>
       </c>
       <c r="D12" t="n">
         <v>16.58065</v>
       </c>
       <c r="E12" t="n">
-        <v>17.06103</v>
+        <v>16.72374</v>
       </c>
       <c r="F12" t="n">
         <v>41.84835</v>
@@ -740,13 +740,13 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>16.7572</v>
+      </c>
+      <c r="D13" t="n">
         <v>16.31855</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>16.32433</v>
-      </c>
-      <c r="E13" t="n">
-        <v>16.7572</v>
       </c>
       <c r="F13" t="n">
         <v>41.72727</v>
@@ -768,10 +768,10 @@
         <v>16.8867</v>
       </c>
       <c r="D14" t="n">
+        <v>16.3867</v>
+      </c>
+      <c r="E14" t="n">
         <v>16.45241</v>
-      </c>
-      <c r="E14" t="n">
-        <v>16.3867</v>
       </c>
       <c r="F14" t="n">
         <v>42.36878</v>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
+        <v>16.83999</v>
+      </c>
+      <c r="D16" t="n">
+        <v>16.46871</v>
+      </c>
+      <c r="E16" t="n">
         <v>16.73347</v>
-      </c>
-      <c r="D16" t="n">
-        <v>16.83999</v>
-      </c>
-      <c r="E16" t="n">
-        <v>16.46871</v>
       </c>
       <c r="F16" t="n">
         <v>42.20487</v>
@@ -840,13 +840,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.68163</v>
+        <v>16.72087</v>
       </c>
       <c r="D17" t="n">
         <v>16.36619</v>
       </c>
       <c r="E17" t="n">
-        <v>16.72087</v>
+        <v>16.68163</v>
       </c>
       <c r="F17" t="n">
         <v>42.49121</v>
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.44263</v>
+        <v>16.63676</v>
       </c>
       <c r="D18" t="n">
         <v>16.29598</v>
       </c>
       <c r="E18" t="n">
-        <v>16.63676</v>
+        <v>16.44263</v>
       </c>
       <c r="F18" t="n">
         <v>42.41792</v>
@@ -893,10 +893,10 @@
         <v>16.54951</v>
       </c>
       <c r="D19" t="n">
+        <v>16.49353</v>
+      </c>
+      <c r="E19" t="n">
         <v>16.53342</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16.49353</v>
       </c>
       <c r="F19" t="n">
         <v>42.40998</v>
